--- a/04_DESIGN_TABLES/DesignTable_6506_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6506_SW2.xlsx
@@ -727,7 +727,7 @@
         <v>0.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AA2" t="n">
         <v>0.2825</v>
@@ -754,7 +754,7 @@
         <v>0.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.025</v>
@@ -797,7 +797,12 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2040 = 1.480 (table had 1.49) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.480 (Items!P2040, M039)</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -813,7 +818,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="C3" t="n">
         <v>0.32332</v>
@@ -906,16 +911,16 @@
         <v>0.21875</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
         <v>0.17</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.505</v>
+        <v>0.575</v>
       </c>
       <c r="AK3" t="n">
         <v>0.5600000000000001</v>
@@ -955,7 +960,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2032 = 1.260 (table had 1.19) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2032 = 0.920 (table had 0.85) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.19 -&gt; OMi 1.260 (Items!L2032, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 0.85 -&gt; OMi 0.920 (Items!P2032, M039)</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -971,7 +981,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="C4" t="n">
         <v>0.43301</v>
@@ -1064,16 +1074,16 @@
         <v>0.21875</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AH4" t="n">
         <v>0.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.755</v>
+        <v>0.835</v>
       </c>
       <c r="AK4" t="n">
         <v>0.5600000000000001</v>
@@ -1113,7 +1123,12 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2033 = 1.520 (table had 1.44) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2033 = 1.170 (table had 1.09) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.44 -&gt; OMi 1.520 (Items!L2033, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.09 -&gt; OMi 1.170 (Items!P2033, M039)</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1129,7 +1144,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="C5" t="n">
         <v>0.43301</v>
@@ -1222,16 +1237,16 @@
         <v>0.28125</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AH5" t="n">
         <v>0.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.715</v>
+        <v>0.845</v>
       </c>
       <c r="AK5" t="n">
         <v>0.6899999999999999</v>
@@ -1271,7 +1286,12 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2034 = 1.630 (table had 1.5) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2034 = 1.260 (table had 1.13) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.5 -&gt; OMi 1.630 (Items!L2034, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.13 -&gt; OMi 1.260 (Items!P2034, M039)</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1287,7 +1307,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="C6" t="n">
         <v>0.50807</v>
@@ -1380,16 +1400,16 @@
         <v>0.28125</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AH6" t="n">
         <v>0.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.845</v>
+        <v>0.905</v>
       </c>
       <c r="AK6" t="n">
         <v>0.6899999999999999</v>
@@ -1429,7 +1449,12 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039)</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1445,7 +1470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1538,16 +1563,16 @@
         <v>0.375</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="n">
         <v>0.39</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.725</v>
+        <v>0.895</v>
       </c>
       <c r="AK7" t="n">
         <v>0.88</v>
@@ -1587,7 +1612,12 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039)</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1603,7 +1633,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="C8" t="n">
         <v>0.65241</v>
@@ -1696,16 +1726,16 @@
         <v>0.28125</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="n">
         <v>0.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.085</v>
+        <v>1.135</v>
       </c>
       <c r="AK8" t="n">
         <v>0.6899999999999999</v>
@@ -1745,7 +1775,12 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039)</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -1761,7 +1796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="C9" t="n">
         <v>0.65241</v>
@@ -1854,16 +1889,16 @@
         <v>0.4375</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="n">
         <v>0.48</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.095</v>
+        <v>1.135</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
@@ -1903,7 +1938,12 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039)</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -1919,7 +1959,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="C10" t="n">
         <v>0.79674</v>
@@ -1991,7 +2031,7 @@
         <v>0.394</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AA10" t="n">
         <v>0.3375</v>
@@ -2012,16 +2052,16 @@
         <v>0.4375</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="n">
         <v>0.48</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.125</v>
+        <v>1.195</v>
       </c>
       <c r="AK10" t="n">
         <v>1</v>
@@ -2061,7 +2101,12 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039)</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -2729,7 +2774,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>1.37409</v>
@@ -2822,16 +2867,16 @@
         <v>0.9375</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
         <v>1.31</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AK15" t="n">
         <v>2.25</v>
@@ -2871,7 +2916,12 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2049 = 3.000 (table had 2.98) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2049 = 2.270 (table had 2.25) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.98 -&gt; OMi 3.000 (Items!L2049, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 2.25 -&gt; OMi 2.270 (Items!P2049, M039)</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6506_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6506_SW2.xlsx
@@ -727,7 +727,7 @@
         <v>0.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AA2" t="n">
         <v>0.2825</v>
@@ -754,7 +754,7 @@
         <v>0.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.025</v>
@@ -797,12 +797,12 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2040 = 1.480 (table had 1.49) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2040 = 1.480 (table had 1.49) [user 2026-10-18 A19]; L18@DRIVE: Air-Way 1.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.480 (Items!P2040, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.480 (Items!P2040, M039) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.48 -&gt; Air-Way 1.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="C3" t="n">
         <v>0.32332</v>
@@ -911,16 +911,16 @@
         <v>0.21875</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
         <v>0.17</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.575</v>
+        <v>0.505</v>
       </c>
       <c r="AK3" t="n">
         <v>0.5600000000000001</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2032 = 1.260 (table had 1.19) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2032 = 0.920 (table had 0.85) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2032 = 1.260 (table had 1.19) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2032 = 0.920 (table had 0.85) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 0.85 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.19 -&gt; OMi 1.260 (Items!L2032, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 0.85 -&gt; OMi 0.920 (Items!P2032, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.19 -&gt; OMi 1.260 (Items!L2032, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 0.85 -&gt; OMi 0.920 (Items!P2032, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.19 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 0.92 -&gt; Air-Way 0.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="C4" t="n">
         <v>0.43301</v>
@@ -1074,16 +1074,16 @@
         <v>0.21875</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
         <v>0.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.835</v>
+        <v>0.755</v>
       </c>
       <c r="AK4" t="n">
         <v>0.5600000000000001</v>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2033 = 1.520 (table had 1.44) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2033 = 1.170 (table had 1.09) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2033 = 1.520 (table had 1.44) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2033 = 1.170 (table had 1.09) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.44 -&gt; OMi 1.520 (Items!L2033, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.09 -&gt; OMi 1.170 (Items!P2033, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.44 -&gt; OMi 1.520 (Items!L2033, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.09 -&gt; OMi 1.170 (Items!P2033, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.52 -&gt; Air-Way 1.44 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.17 -&gt; Air-Way 1.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="C5" t="n">
         <v>0.43301</v>
@@ -1237,16 +1237,16 @@
         <v>0.28125</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
         <v>0.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.845</v>
+        <v>0.715</v>
       </c>
       <c r="AK5" t="n">
         <v>0.6899999999999999</v>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2034 = 1.630 (table had 1.5) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2034 = 1.260 (table had 1.13) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2034 = 1.630 (table had 1.5) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2034 = 1.260 (table had 1.13) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.63) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.5 -&gt; OMi 1.630 (Items!L2034, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.13 -&gt; OMi 1.260 (Items!P2034, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.5 -&gt; OMi 1.630 (Items!L2034, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.13 -&gt; OMi 1.260 (Items!P2034, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.63 -&gt; Air-Way 1.5 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="C6" t="n">
         <v>0.50807</v>
@@ -1400,16 +1400,16 @@
         <v>0.28125</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AH6" t="n">
         <v>0.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.905</v>
+        <v>0.845</v>
       </c>
       <c r="AK6" t="n">
         <v>0.6899999999999999</v>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.31) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.63 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.31 -&gt; Air-Way 1.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1563,16 +1563,16 @@
         <v>0.375</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AH7" t="n">
         <v>0.39</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.895</v>
+        <v>0.725</v>
       </c>
       <c r="AK7" t="n">
         <v>0.88</v>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.61 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.61 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="C8" t="n">
         <v>0.65241</v>
@@ -1726,16 +1726,16 @@
         <v>0.28125</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="n">
         <v>0.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.135</v>
+        <v>1.085</v>
       </c>
       <c r="AK8" t="n">
         <v>0.6899999999999999</v>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.87 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.54) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.92 -&gt; Air-Way 1.87 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.54 -&gt; Air-Way 1.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="C9" t="n">
         <v>0.65241</v>
@@ -1889,16 +1889,16 @@
         <v>0.4375</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="n">
         <v>0.48</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.135</v>
+        <v>1.095</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.08 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="C10" t="n">
         <v>0.79674</v>
@@ -2031,7 +2031,7 @@
         <v>0.394</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AA10" t="n">
         <v>0.3375</v>
@@ -2052,16 +2052,16 @@
         <v>0.4375</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AH10" t="n">
         <v>0.48</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.195</v>
+        <v>1.125</v>
       </c>
       <c r="AK10" t="n">
         <v>1</v>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.62 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.11 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.68 -&gt; Air-Way 1.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -2194,7 +2194,7 @@
         <v>0.481</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="AA11" t="n">
         <v>0.4225</v>
@@ -2221,7 +2221,7 @@
         <v>0.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.191</v>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2044 Overall Length = 2.280 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2044 L 1 Size = 1.720 (table had 1.57) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2044 / V2044 / X2044 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2044 Overall Length = 2.280 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2044 L 1 Size = 1.720 (table had 1.57) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2044 / V2044 / X2044 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 1.57 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2044 2.280, L18 = OMi Items!P2044 1.720 (was Air-Way 1.57) -&gt; ASSUMED; catalog TFA p18 L5 2.29 / L2 1.72 (L5 vs OMi 2.280: 0.01 inside the one source - OMi first)</t>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2044 2.280, L18 = OMi Items!P2044 1.720 (was Air-Way 1.57) -&gt; ASSUMED; catalog TFA p18 L5 2.29 / L2 1.72 (L5 vs OMi 2.280: 0.01 inside the one source - OMi first) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.57 | Air-Way nut-face-to-seat 0.710 vs Brennan 0.570</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>0.604</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="AA13" t="n">
         <v>0.5475</v>
@@ -2547,7 +2547,7 @@
         <v>0.84</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.435</v>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2047 Overall Length = 2.610 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2047 L 1 Size = 2.020 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2047 / V2047 / X2047 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2047 Overall Length = 2.610 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2047 L 1 Size = 2.020 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2047 / V2047 / X2047 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2047 2.610, L18 = OMi Items!P2047 2.020 (was Air-Way 2.03) -&gt; ASSUMED; catalog TFA p18 L5 2.614 / L2 2.02 (2.614 vs OMi 2.610: rounding only)</t>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2047 2.610, L18 = OMi Items!P2047 2.020 (was Air-Way 2.03) -&gt; ASSUMED; catalog TFA p18 L5 2.614 / L2 2.02 (2.614 vs OMi 2.610: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.02 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -2683,7 +2683,7 @@
         <v>0.766</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="AA14" t="n">
         <v>0.7025</v>
@@ -2710,7 +2710,7 @@
         <v>1.08</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.57</v>
@@ -2753,12 +2753,12 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2048 Overall Length = 2.830 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2048 L 1 Size = 2.200 (table had 2.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2048 / V2048 / X2048 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2048 Overall Length = 2.830 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2048 L 1 Size = 2.200 (table had 2.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2048 / V2048 / X2048 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2048 2.830, L18 = OMi Items!P2048 2.200 (was Air-Way 2.13) -&gt; ASSUMED; catalog TFA p18 L5 2.825 / L2 2.200 (2.825 vs OMi 2.830: rounding only)</t>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2048 2.830, L18 = OMi Items!P2048 2.200 (was Air-Way 2.13) -&gt; ASSUMED; catalog TFA p18 L5 2.825 / L2 2.200 (2.825 vs OMi 2.830: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.2 -&gt; Air-Way 2.13 | Air-Way nut-face-to-seat 0.700 vs Brennan 0.640</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="C15" t="n">
         <v>1.37409</v>
@@ -2867,16 +2867,16 @@
         <v>0.9375</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AH15" t="n">
         <v>1.31</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AK15" t="n">
         <v>2.25</v>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2049 = 3.000 (table had 2.98) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2049 = 2.270 (table had 2.25) [user 2026-10-18 A19] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2049 = 3.000 (table had 2.98) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2049 = 2.270 (table had 2.25) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.98 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 2.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.98 -&gt; OMi 3.000 (Items!L2049, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 2.25 -&gt; OMi 2.270 (Items!P2049, M039)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.98 -&gt; OMi 3.000 (Items!L2049, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 2.25 -&gt; OMi 2.270 (Items!P2049, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 3 -&gt; Air-Way 2.98 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.27 -&gt; Air-Way 2.25</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6506_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6506_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU15"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,17 +1303,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6506-06-06</t>
+          <t>6506-06-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="C6" t="n">
-        <v>0.50807</v>
+        <v>0.50518</v>
       </c>
       <c r="D6" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="E6" t="n">
         <v>0.57</v>
@@ -1337,94 +1337,94 @@
         <v>0.3294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.785</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.206</v>
+        <v>0.1465</v>
       </c>
       <c r="N6" t="n">
-        <v>0.735</v>
+        <v>0.649</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3224</v>
+        <v>0.2574</v>
       </c>
       <c r="P6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA6" t="n">
         <v>0.145</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.3428</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.3876</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.39837</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.28125</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.25118</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.2945</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.2925</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.5953000000000001</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.215</v>
-      </c>
       <c r="AB6" t="n">
-        <v>0.50236</v>
+        <v>0.38338</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3197</v>
+        <v>0.2867</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.25118</v>
+        <v>0.19169</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.3</v>
+        <v>0.172</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.845</v>
+        <v>0.905</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.3876</v>
+        <v>0.3268</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>6506-06-06</t>
+          <t>6506-06-04</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 3/8-18 NPTF (female) x 9/16-18 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/8-18 NPTF (female) x 7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC swivel)</t>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1449,28 +1449,28 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.31) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L17 / L18 / hex / nut hex / D = OMi WebsitePartsInfo2026.xlsx Items row 2035; column reading L17 = OMi "Overall Length" (port face to the swivel-nut face), L18 = OMi "L 1" (to the seat) - Q-B-SWSTR, settled by the Brennan TFA p18 letters L5 / L2 (batch 15); tap drill 0.57 = Air-Way per size (A1); thread majors from the end library; cross-check Brennan TFA p18 6506-06-04: L5 1.59 / L2 1.24 / C4 HEX 0.875 / C HEX 0.563 / A DRILL 0.172 - equal or rounding; no $PRP@DimSource column in this table - source = OMI | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.63 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.31 -&gt; Air-Way 1.25</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 2035 + A1 tap drill; cross-check Brennan TFA p18 6506-06-04: L5 1.59 / L2 1.24 / C4 HEX 0.875 / C HEX 0.563 / A DRILL 0.172 - equal or rounding</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>6506-06-06</t>
+          <t>6506-06-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6506-06-08</t>
+          <t>6506-06-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1500,94 +1500,94 @@
         <v>0.3294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.885</v>
+        <v>0.785</v>
       </c>
       <c r="M7" t="n">
-        <v>0.292</v>
+        <v>0.206</v>
       </c>
       <c r="N7" t="n">
-        <v>0.827</v>
+        <v>0.735</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4108</v>
+        <v>0.3224</v>
       </c>
       <c r="P7" t="n">
-        <v>0.18</v>
+        <v>0.145</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4361</v>
+        <v>0.3428</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="T7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="U7" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3283</v>
+        <v>0.2945</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3925</v>
+        <v>0.2925</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6723</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.34</v>
+        <v>0.246</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2825</v>
+        <v>0.215</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3567</v>
+        <v>0.3197</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.725</v>
+        <v>0.845</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>6506-06-08</t>
+          <t>6506-06-06</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 3/8-18 NPTF (female) x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/8-18 NPTF (female) x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1612,145 +1612,145 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.61 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2036 = 1.690 (table had 1.63) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2036 = 1.310 (table had 1.25) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.31) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.61 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.19</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.63 -&gt; OMi 1.690 (Items!L2036, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.25 -&gt; OMi 1.310 (Items!P2036, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.63 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.31 -&gt; Air-Way 1.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>6506-06-08</t>
+          <t>6506-06-06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6506-08-06</t>
+          <t>6506-06-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="C8" t="n">
-        <v>0.65241</v>
+        <v>0.50807</v>
       </c>
       <c r="D8" t="n">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="L8" t="n">
-        <v>0.785</v>
+        <v>0.885</v>
       </c>
       <c r="M8" t="n">
-        <v>0.206</v>
+        <v>0.292</v>
       </c>
       <c r="N8" t="n">
-        <v>0.735</v>
+        <v>0.827</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3224</v>
+        <v>0.4108</v>
       </c>
       <c r="P8" t="n">
-        <v>0.145</v>
+        <v>0.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3428</v>
+        <v>0.4361</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3876</v>
+        <v>0.4499</v>
       </c>
       <c r="S8" t="n">
-        <v>0.39837</v>
+        <v>0.50807</v>
       </c>
       <c r="T8" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="U8" t="n">
-        <v>0.25118</v>
+        <v>0.34117</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2945</v>
+        <v>0.3283</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2925</v>
+        <v>0.3925</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.6723</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.246</v>
+        <v>0.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.215</v>
+        <v>0.2825</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.50236</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3197</v>
+        <v>0.3567</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.25118</v>
+        <v>0.34117</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.085</v>
+        <v>0.725</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.3876</v>
+        <v>0.4499</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6506-08-06</t>
+          <t>6506-06-08</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 1/2-14 NPTF (female) x 9/16-18 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/8-18 NPTF (female) x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1775,55 +1775,55 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.87 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.54) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2037 = 1.780 (table had 1.61) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2037 = 1.360 (table had 1.19) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.61 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.92 -&gt; Air-Way 1.87 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.54 -&gt; Air-Way 1.49</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.61 -&gt; OMi 1.780 (Items!L2037, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.19 -&gt; OMi 1.360 (Items!P2037, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.61 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>6506-08-06</t>
+          <t>6506-06-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6506-08-10</t>
+          <t>6506-06-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="C9" t="n">
-        <v>0.65241</v>
+        <v>0.54155</v>
       </c>
       <c r="D9" t="n">
-        <v>1.13</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="J9" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="L9" t="n">
         <v>0.985</v>
@@ -1889,16 +1889,16 @@
         <v>0.4375</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.48</v>
+        <v>0.484</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.095</v>
+        <v>0.915</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6506-08-10</t>
+          <t>6506-06-10</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 1/2-14 NPTF (female) x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/8-18 NPTF (female) x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -1938,145 +1938,145 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L17 / L18 / hex / nut hex / D = OMi WebsitePartsInfo2026.xlsx Items row 2038; column reading L17 = OMi "Overall Length" (port face to the swivel-nut face), L18 = OMi "L 1" (to the seat) - Q-B-SWSTR, settled by the Brennan TFA p18 letters L5 / L2 (batch 15); tap drill 0.57 = Air-Way per size (A1); thread majors from the end library; OMi Side 1 Thread prints "1/2- 14 NPTF" - a misprint: its own Side 1 Size " 3/8 ", the part number -06 and Brennan p18 (3/8-18) give 3/8-18 (Q-THREAD: the part number's thread); cross-check Brennan TFA p18 6506-06-10: L5 1.900 / L2 1.400 / C4 HEX 0.938 / C HEX 1.000 / A DRILL 0.484 - equal; no $PRP@DimSource column in this table - source = OMI | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.08 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.58</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 2038 + A1 tap drill; cross-check Brennan TFA p18 6506-06-10: L5 1.900 / L2 1.400 / C4 HEX 0.938 / C HEX 1.000 / A DRILL 0.484 - equal | OMi thread text misprint (1/2-14) - 3/8-18 used</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>6506-08-10</t>
+          <t>6506-06-10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6506-12-10</t>
+          <t>6506-08-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="C10" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D10" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L10" t="n">
-        <v>0.985</v>
+        <v>0.785</v>
       </c>
       <c r="M10" t="n">
-        <v>0.347</v>
+        <v>0.206</v>
       </c>
       <c r="N10" t="n">
-        <v>0.944</v>
+        <v>0.735</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4758</v>
+        <v>0.3224</v>
       </c>
       <c r="P10" t="n">
-        <v>0.19</v>
+        <v>0.145</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4988</v>
+        <v>0.3428</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>0.57735</v>
+        <v>0.39837</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="U10" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="V10" t="n">
-        <v>0.404</v>
+        <v>0.2945</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4475</v>
+        <v>0.2925</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7794</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.394</v>
+        <v>0.246</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3375</v>
+        <v>0.215</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4364</v>
+        <v>0.3197</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.125</v>
+        <v>1.085</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6506-12-10</t>
+          <t>6506-08-06</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 3/4-14 NPTF (female) x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 1/2-14 NPTF (female) x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2101,145 +2101,145 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.62 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2039 = 1.920 (table had 1.87) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2039 = 1.540 (table had 1.49) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 1.87 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.92) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.54) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.11 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.68 -&gt; Air-Way 1.62</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 1.87 -&gt; OMi 1.920 (Items!L2039, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.49 -&gt; OMi 1.540 (Items!P2039, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 1.92 -&gt; Air-Way 1.87 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.54 -&gt; Air-Way 1.49</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>6506-12-10</t>
+          <t>6506-08-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6506-12-12</t>
+          <t>6506-08-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="C11" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D11" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H11" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L11" t="n">
-        <v>1.089</v>
+        <v>0.985</v>
       </c>
       <c r="M11" t="n">
-        <v>0.417</v>
+        <v>0.347</v>
       </c>
       <c r="N11" t="n">
-        <v>1.047</v>
+        <v>0.944</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5928</v>
+        <v>0.4758</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6237</v>
+        <v>0.4988</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="T11" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="U11" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4472</v>
+        <v>0.404</v>
       </c>
       <c r="W11" t="n">
-        <v>0.549</v>
+        <v>0.4475</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8623</v>
+        <v>0.7794</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.481</v>
+        <v>0.394</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4225</v>
+        <v>0.3375</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.97228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4851</v>
+        <v>0.4364</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.191</v>
+        <v>1.095</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6506-12-12</t>
+          <t>6506-08-10</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 3/4-14 NPTF (female) x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 1/2-14 NPTF (female) x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -2264,34 +2264,34 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2044 Overall Length = 2.280 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2044 L 1 Size = 1.720 (table had 1.57) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2044 / V2044 / X2044 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 1.57 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2041 = 2.120 (table had 2.08) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2041 = 1.620 (table had 1.58) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2044 2.280, L18 = OMi Items!P2044 1.720 (was Air-Way 1.57) -&gt; ASSUMED; catalog TFA p18 L5 2.29 / L2 1.72 (L5 vs OMi 2.280: 0.01 inside the one source - OMi first) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.57 | Air-Way nut-face-to-seat 0.710 vs Brennan 0.570</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.08 -&gt; OMi 2.120 (Items!L2041, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.58 -&gt; OMi 1.620 (Items!P2041, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.08 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>6506-12-12</t>
+          <t>6506-08-10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6506-12-16</t>
+          <t>6506-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="C12" t="n">
-        <v>0.79674</v>
+        <v>0.79386</v>
       </c>
       <c r="D12" t="n">
-        <v>1.38</v>
+        <v>1.375</v>
       </c>
       <c r="E12" t="n">
         <v>0.91</v>
@@ -2315,94 +2315,94 @@
         <v>0.5121</v>
       </c>
       <c r="L12" t="n">
-        <v>1.175</v>
+        <v>0.885</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5485</v>
+        <v>0.292</v>
       </c>
       <c r="N12" t="n">
-        <v>1.139</v>
+        <v>0.827</v>
       </c>
       <c r="O12" t="n">
-        <v>0.727</v>
+        <v>0.4108</v>
       </c>
       <c r="P12" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.749</v>
+        <v>0.4361</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6564</v>
+        <v>0.4499</v>
       </c>
       <c r="S12" t="n">
-        <v>0.86603</v>
+        <v>0.50518</v>
       </c>
       <c r="T12" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="U12" t="n">
-        <v>0.61114</v>
+        <v>0.34117</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4873</v>
+        <v>0.3283</v>
       </c>
       <c r="W12" t="n">
-        <v>0.665</v>
+        <v>0.3925</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9544</v>
+        <v>0.6723</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.604</v>
+        <v>0.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5475</v>
+        <v>0.2825</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22228</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.5252</v>
+        <v>0.3567</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.61114</v>
+        <v>0.34117</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.84</v>
+        <v>0.391</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.025</v>
+        <v>1.185</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0.875</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.6564</v>
+        <v>0.4499</v>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6506-12-16</t>
+          <t>6506-12-08</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 3/4-14 NPTF (female) x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/4-14 NPTF (female) x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2427,145 +2427,145 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2046 Overall Length = 2.200 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE unchanged: OMi Items!P2046 L 1 Size = 1.610 = Air-Way 1.61; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2046 / V2046 / X2046 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L17 / L18 / hex / nut hex / D = OMi WebsitePartsInfo2026.xlsx Items row 2042; column reading L17 = OMi "Overall Length" (port face to the swivel-nut face), L18 = OMi "L 1" (to the seat) - Q-B-SWSTR, settled by the Brennan TFA p18 letters L5 / L2 (batch 15); tap drill 0.91 = Air-Way per size (A1); thread majors from the end library; not printed in the Brennan TFA catalog; no $PRP@DimSource column in this table - source = OMI | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2046 2.200 -&gt; ASSUMED; catalog TFA p18 L5 2.200 / L2 1.610 = OMi</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 2042 + A1 tap drill; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>6506-12-16</t>
+          <t>6506-12-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6506-16-16</t>
+          <t>6506-12-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.61</v>
+        <v>2.11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D13" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="F13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="G13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="H13" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="L13" t="n">
-        <v>1.175</v>
+        <v>0.985</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5485</v>
+        <v>0.347</v>
       </c>
       <c r="N13" t="n">
-        <v>1.139</v>
+        <v>0.944</v>
       </c>
       <c r="O13" t="n">
-        <v>0.727</v>
+        <v>0.4758</v>
       </c>
       <c r="P13" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.4988</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6564</v>
+        <v>0.5265</v>
       </c>
       <c r="S13" t="n">
-        <v>0.86603</v>
+        <v>0.57735</v>
       </c>
       <c r="T13" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="U13" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4873</v>
+        <v>0.404</v>
       </c>
       <c r="W13" t="n">
-        <v>0.665</v>
+        <v>0.4475</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9544</v>
+        <v>0.7794</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.604</v>
+        <v>0.394</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5475</v>
+        <v>0.3375</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5252</v>
+        <v>0.4364</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.61</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.435</v>
+        <v>1.125</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.6564</v>
+        <v>0.5265</v>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>6506-16-16</t>
+          <t>6506-12-10</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF (female) x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/4-14 NPTF (female) x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -2590,145 +2590,145 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2047 Overall Length = 2.610 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2047 L 1 Size = 2.020 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2047 / V2047 / X2047 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2043 = 2.180 (table had 2.11) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2043 = 1.680 (table had 1.62) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 1.62 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2047 2.610, L18 = OMi Items!P2047 2.020 (was Air-Way 2.03) -&gt; ASSUMED; catalog TFA p18 L5 2.614 / L2 2.02 (2.614 vs OMi 2.610: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.02 -&gt; Air-Way 2.03</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.11 -&gt; OMi 2.180 (Items!L2043, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 1.62 -&gt; OMi 1.680 (Items!P2043, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.11 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.68 -&gt; Air-Way 1.62</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>6506-16-16</t>
+          <t>6506-12-10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6506-20-20</t>
+          <t>6506-12-12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.83</v>
+        <v>2.28</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1547</v>
+        <v>0.79674</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="E14" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="F14" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="G14" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="H14" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.74</v>
+        <v>0.455</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8096</v>
+        <v>0.5121</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.089</v>
       </c>
       <c r="M14" t="n">
-        <v>0.68</v>
+        <v>0.417</v>
       </c>
       <c r="N14" t="n">
-        <v>1.145</v>
+        <v>1.047</v>
       </c>
       <c r="O14" t="n">
-        <v>0.949</v>
+        <v>0.5928</v>
       </c>
       <c r="P14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9889</v>
+        <v>0.6237</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5375</v>
+        <v>0.5998</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1547</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="U14" t="n">
-        <v>0.76739</v>
+        <v>0.48614</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4345</v>
+        <v>0.4472</v>
       </c>
       <c r="W14" t="n">
-        <v>0.88</v>
+        <v>0.549</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9556</v>
+        <v>0.8623</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.766</v>
+        <v>0.481</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.7025</v>
+        <v>0.4225</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53478</v>
+        <v>0.97228</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.4724</v>
+        <v>0.4851</v>
       </c>
       <c r="AD14" t="n">
         <v>0.08333</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.76739</v>
+        <v>0.48614</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.83</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.57</v>
+        <v>1.191</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.5375</v>
+        <v>0.5998</v>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>6506-20-20</t>
+          <t>6506-12-12</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Female Pipe x Female JIC Swivel Connector, 1 1/4-11 1/2 NPTF (female) x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/4-14 NPTF (female) x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -2753,178 +2753,667 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2048 Overall Length = 2.830 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2048 L 1 Size = 2.200 (table had 2.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2048 / V2048 / X2048 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2044 Overall Length = 2.280 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2044 L 1 Size = 1.720 (table had 1.57) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2044 / V2044 / X2044 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 1.57 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2048 2.830, L18 = OMi Items!P2048 2.200 (was Air-Way 2.13) -&gt; ASSUMED; catalog TFA p18 L5 2.825 / L2 2.200 (2.825 vs OMi 2.830: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.2 -&gt; Air-Way 2.13 | Air-Way nut-face-to-seat 0.700 vs Brennan 0.640</t>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2044 2.280, L18 = OMi Items!P2044 1.720 (was Air-Way 1.57) -&gt; ASSUMED; catalog TFA p18 L5 2.29 / L2 1.72 (L5 vs OMi 2.280: 0.01 inside the one source - OMi first) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.57 | Air-Way nut-face-to-seat 0.710 vs Brennan 0.570</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>6506-20-20</t>
+          <t>6506-12-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6506-24-24</t>
+          <t>6506-12-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.98</v>
+        <v>2.2</v>
       </c>
       <c r="C15" t="n">
-        <v>1.37409</v>
+        <v>0.79674</v>
       </c>
       <c r="D15" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="E15" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="F15" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>0.91</v>
       </c>
       <c r="H15" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.86</v>
+        <v>0.455</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9296</v>
+        <v>0.5121</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.175</v>
       </c>
       <c r="M15" t="n">
-        <v>0.776</v>
+        <v>0.5485</v>
       </c>
       <c r="N15" t="n">
-        <v>1.32</v>
+        <v>1.139</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0504</v>
+        <v>0.727</v>
       </c>
       <c r="P15" t="n">
         <v>0.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.1134</v>
+        <v>0.749</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7063</v>
+        <v>0.6564</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29904</v>
+        <v>0.86603</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="U15" t="n">
-        <v>0.89239</v>
+        <v>0.61114</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5295</v>
+        <v>0.4873</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>0.665</v>
       </c>
       <c r="X15" t="n">
-        <v>1.065</v>
+        <v>0.9544</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.8885</v>
+        <v>0.604</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5475</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78478</v>
+        <v>1.22228</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5674</v>
+        <v>0.5252</v>
       </c>
       <c r="AD15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AE15" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>6506-12-16</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Female Pipe x Female JIC Swivel Connector, 3/4-14 NPTF (female) x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2046 Overall Length = 2.200 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE unchanged: OMi Items!P2046 L 1 Size = 1.610 = Air-Way 1.61; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2046 / V2046 / X2046 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2046 2.200 -&gt; ASSUMED; catalog TFA p18 L5 2.200 / L2 1.610 = OMi</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>6506-12-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6506-16-16</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.94108</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>6506-16-16</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Female Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF (female) x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2047 Overall Length = 2.610 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2047 L 1 Size = 2.020 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2047 / V2047 / X2047 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2047 2.610, L18 = OMi Items!P2047 2.020 (was Air-Way 2.03) -&gt; ASSUMED; catalog TFA p18 L5 2.614 / L2 2.02 (2.614 vs OMi 2.610: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.02 -&gt; Air-Way 2.03</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>6506-16-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6506-20-20</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>6506-20-20</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Female Pipe x Female JIC Swivel Connector, 1 1/4-11 1/2 NPTF (female) x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2048 Overall Length = 2.830 (table had empty: blank on Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2048 L 1 Size = 2.200 (table had 2.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; column reading: OMi Overall Length = port face to swivel-nut face (L17), L 1 = port face to stem nose / seat (L18), settled by the Brennan TFA catalog p18 6506 drawing letters L5 / L2 (Q-B-SWSTR, impact F45D); C1HEX / C3HEX / D: OMi Items!R2048 / V2048 / X2048 equal Air-Way or rounding-only (no change); TAPDRILL Air-Way - batch 15, 2026-10-02 (staged, not shipped); L18@DRIVE: Air-Way 2.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>L17: blank on Air-Way -&gt; MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): L17 = OMi Items!L2048 2.830, L18 = OMi Items!P2048 2.200 (was Air-Way 2.13) -&gt; ASSUMED; catalog TFA p18 L5 2.825 / L2 2.200 (2.825 vs OMi 2.830: rounding only) | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.2 -&gt; Air-Way 2.13 | Air-Way nut-face-to-seat 0.700 vs Brennan 0.640</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>6506-20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6506-24-24</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.37409</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.0504</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.89239</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="V18" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0.9375</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG18" t="n">
         <v>2.98</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AH18" t="n">
         <v>1.31</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI18" t="n">
         <v>2.25</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AJ18" t="n">
         <v>1.57</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK18" t="n">
         <v>2.25</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL18" t="n">
         <v>0.7063</v>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>6506-24-24</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>Female Pipe x Female JIC Swivel Connector, 1 1/2-11 1/2 NPTF (female) x 1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>6506</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>1 1/2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>1 7/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AR18" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>Air-Way s102 only (double-pass 18 rows); L17@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2049 = 3.000 (table had 2.98) [user 2026-10-18 A19]; L18@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2049 = 2.270 (table had 2.25) [user 2026-10-18 A19]; L17@DRIVE: Air-Way 2.98 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L18@DRIVE: Air-Way 2.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs at -04/-08/-12/-16), tapered helical thread over P1; L17 = port face to the nut face, L18 = port face to the seat; body hex C1, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D from the port bottom to the seat</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>A19 (user 2026-10-18, group 2 settled): L17@DRIVE 2.98 -&gt; OMi 3.000 (Items!L2049, M038) | A19 (user 2026-10-18, group 2 settled): L18@DRIVE 2.25 -&gt; OMi 2.270 (Items!P2049, M039) | 2026-10-20 Air-Way first: L17@DRIVE OMi/Brennan 3 -&gt; Air-Way 2.98 | 2026-10-20 Air-Way first: L18@DRIVE OMi/Brennan 2.27 -&gt; Air-Way 2.25</t>
         </is>
       </c>
-      <c r="AU15" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>6506-24-24</t>
         </is>
